--- a/ojt_files/6140.xlsx
+++ b/ojt_files/6140.xlsx
@@ -1,642 +1,662 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="report" sheetId="1" r:id="rId1"/>
+    <sheet name="report" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="199">
-  <si>
-    <t>Transaction</t>
-  </si>
-  <si>
-    <t>Employee ID</t>
-  </si>
-  <si>
-    <t>First Name</t>
-  </si>
-  <si>
-    <t>Department</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Punch Time</t>
-  </si>
-  <si>
-    <t>Punch State</t>
-  </si>
-  <si>
-    <t>Area</t>
-  </si>
-  <si>
-    <t>Serial Number</t>
-  </si>
-  <si>
-    <t>Device Name</t>
-  </si>
-  <si>
-    <t>Upload Time</t>
-  </si>
-  <si>
-    <t>Actual Temperature</t>
-  </si>
-  <si>
-    <t>6140</t>
-  </si>
-  <si>
-    <t>2026-06-24</t>
-  </si>
-  <si>
-    <t>07:38:00</t>
-  </si>
-  <si>
-    <t>Check In</t>
-  </si>
-  <si>
-    <t>Main Office</t>
-  </si>
-  <si>
-    <t>5870221760077</t>
-  </si>
-  <si>
-    <t>HR Office</t>
-  </si>
-  <si>
-    <t>2026-06-24 07:37:57</t>
-  </si>
-  <si>
-    <t>2026-06-23</t>
-  </si>
-  <si>
-    <t>17:08:40</t>
-  </si>
-  <si>
-    <t>Check Out</t>
-  </si>
-  <si>
-    <t>5870201460003</t>
-  </si>
-  <si>
-    <t>Board/Function Room</t>
-  </si>
-  <si>
-    <t>2026-06-23 17:08:37</t>
-  </si>
-  <si>
-    <t>12:50:02</t>
-  </si>
-  <si>
-    <t>2026-06-23 12:50:00</t>
-  </si>
-  <si>
-    <t>12:03:36</t>
-  </si>
-  <si>
-    <t>2026-06-23 12:03:33</t>
-  </si>
-  <si>
-    <t>07:39:13</t>
-  </si>
-  <si>
-    <t>2026-06-23 07:39:11</t>
-  </si>
-  <si>
-    <t>2026-06-22</t>
-  </si>
-  <si>
-    <t>17:04:21</t>
-  </si>
-  <si>
-    <t>2026-06-22 17:04:18</t>
-  </si>
-  <si>
-    <t>12:28:46</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:28:44</t>
-  </si>
-  <si>
-    <t>12:04:11</t>
-  </si>
-  <si>
-    <t>2026-06-22 12:04:09</t>
-  </si>
-  <si>
-    <t>07:03:50</t>
-  </si>
-  <si>
-    <t>2026-06-22 07:03:48</t>
-  </si>
-  <si>
-    <t>2026-06-20</t>
-  </si>
-  <si>
-    <t>17:00:41</t>
-  </si>
-  <si>
-    <t>2026-06-20 17:00:41</t>
-  </si>
-  <si>
-    <t>12:33:11</t>
-  </si>
-  <si>
-    <t>2026-06-20 12:33:09</t>
-  </si>
-  <si>
-    <t>12:04:05</t>
-  </si>
-  <si>
-    <t>2026-06-20 12:04:06</t>
-  </si>
-  <si>
-    <t>07:38:11</t>
-  </si>
-  <si>
-    <t>2026-06-20 07:38:10</t>
-  </si>
-  <si>
-    <t>2026-06-19</t>
-  </si>
-  <si>
-    <t>17:03:12</t>
-  </si>
-  <si>
-    <t>2026-06-19 17:03:14</t>
-  </si>
-  <si>
-    <t>12:21:14</t>
-  </si>
-  <si>
-    <t>2026-06-19 12:21:17</t>
-  </si>
-  <si>
-    <t>12:01:25</t>
-  </si>
-  <si>
-    <t>2026-06-19 12:01:27</t>
-  </si>
-  <si>
-    <t>07:42:50</t>
-  </si>
-  <si>
-    <t>2026-06-19 07:42:48</t>
-  </si>
-  <si>
-    <t>2026-06-18</t>
-  </si>
-  <si>
-    <t>17:07:14</t>
-  </si>
-  <si>
-    <t>2026-06-18 17:07:18</t>
-  </si>
-  <si>
-    <t>12:18:19</t>
-  </si>
-  <si>
-    <t>2026-06-18 12:18:23</t>
-  </si>
-  <si>
-    <t>12:01:50</t>
-  </si>
-  <si>
-    <t>2026-06-18 12:01:54</t>
-  </si>
-  <si>
-    <t>07:38:13</t>
-  </si>
-  <si>
-    <t>2026-06-18 07:38:13</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>17:12:11</t>
-  </si>
-  <si>
-    <t>2026-06-17 17:12:04</t>
-  </si>
-  <si>
-    <t>12:40:25</t>
-  </si>
-  <si>
-    <t>2026-06-17 12:40:17</t>
-  </si>
-  <si>
-    <t>12:01:45</t>
-  </si>
-  <si>
-    <t>2026-06-17 12:01:38</t>
-  </si>
-  <si>
-    <t>07:09:24</t>
-  </si>
-  <si>
-    <t>2026-06-17 07:09:24</t>
-  </si>
-  <si>
-    <t>2026-06-15</t>
-  </si>
-  <si>
-    <t>17:01:51</t>
-  </si>
-  <si>
-    <t>2026-06-15 17:01:47</t>
-  </si>
-  <si>
-    <t>12:35:41</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:35:36</t>
-  </si>
-  <si>
-    <t>12:05:08</t>
-  </si>
-  <si>
-    <t>2026-06-15 12:05:09</t>
-  </si>
-  <si>
-    <t>07:02:02</t>
-  </si>
-  <si>
-    <t>2026-06-15 07:02:02</t>
-  </si>
-  <si>
-    <t>2026-06-13</t>
-  </si>
-  <si>
-    <t>17:03:04</t>
-  </si>
-  <si>
-    <t>2026-06-13 17:03:02</t>
-  </si>
-  <si>
-    <t>12:28:49</t>
-  </si>
-  <si>
-    <t>2026-06-13 12:28:49</t>
-  </si>
-  <si>
-    <t>12:03:23</t>
-  </si>
-  <si>
-    <t>2026-06-13 12:03:21</t>
-  </si>
-  <si>
-    <t>07:32:56</t>
-  </si>
-  <si>
-    <t>2026-06-13 07:32:57</t>
-  </si>
-  <si>
-    <t>2026-06-11</t>
-  </si>
-  <si>
-    <t>17:02:06</t>
-  </si>
-  <si>
-    <t>2026-06-11 17:02:08</t>
-  </si>
-  <si>
-    <t>12:43:24</t>
-  </si>
-  <si>
-    <t>2026-06-11 12:43:22</t>
-  </si>
-  <si>
-    <t>12:04:39</t>
-  </si>
-  <si>
-    <t>2026-06-11 12:04:37</t>
-  </si>
-  <si>
-    <t>07:29:20</t>
-  </si>
-  <si>
-    <t>2026-06-11 07:29:25</t>
-  </si>
-  <si>
-    <t>2026-06-10</t>
-  </si>
-  <si>
-    <t>17:05:14</t>
-  </si>
-  <si>
-    <t>2026-06-10 17:05:13</t>
-  </si>
-  <si>
-    <t>12:26:42</t>
-  </si>
-  <si>
-    <t>2026-06-10 12:26:47</t>
-  </si>
-  <si>
-    <t>12:03:09</t>
-  </si>
-  <si>
-    <t>2026-06-10 12:03:15</t>
-  </si>
-  <si>
-    <t>07:24:24</t>
-  </si>
-  <si>
-    <t>2026-06-10 07:24:28</t>
-  </si>
-  <si>
-    <t>2026-06-09</t>
-  </si>
-  <si>
-    <t>17:04:55</t>
-  </si>
-  <si>
-    <t>2026-06-09 17:04:55</t>
-  </si>
-  <si>
-    <t>17:04:45</t>
-  </si>
-  <si>
-    <t>2026-06-09 17:04:46</t>
-  </si>
-  <si>
-    <t>12:30:06</t>
-  </si>
-  <si>
-    <t>2026-06-09 12:30:13</t>
-  </si>
-  <si>
-    <t>12:04:01</t>
-  </si>
-  <si>
-    <t>2026-06-09 12:04:06</t>
-  </si>
-  <si>
-    <t>07:48:51</t>
-  </si>
-  <si>
-    <t>2026-06-09 07:48:57</t>
-  </si>
-  <si>
-    <t>2026-06-08</t>
-  </si>
-  <si>
-    <t>17:01:36</t>
-  </si>
-  <si>
-    <t>2026-06-08 17:01:42</t>
-  </si>
-  <si>
-    <t>12:29:35</t>
-  </si>
-  <si>
-    <t>2026-06-08 12:29:41</t>
-  </si>
-  <si>
-    <t>12:03:37</t>
-  </si>
-  <si>
-    <t>2026-06-08 12:03:28</t>
-  </si>
-  <si>
-    <t>07:13:36</t>
-  </si>
-  <si>
-    <t>2026-06-08 07:13:43</t>
-  </si>
-  <si>
-    <t>2026-06-06</t>
-  </si>
-  <si>
-    <t>17:02:21</t>
-  </si>
-  <si>
-    <t>2026-06-06 17:02:27</t>
-  </si>
-  <si>
-    <t>12:32:15</t>
-  </si>
-  <si>
-    <t>2026-06-06 12:32:22</t>
-  </si>
-  <si>
-    <t>12:02:55</t>
-  </si>
-  <si>
-    <t>2026-06-06 12:03:01</t>
-  </si>
-  <si>
-    <t>07:46:03</t>
-  </si>
-  <si>
-    <t>2026-06-06 07:46:09</t>
-  </si>
-  <si>
-    <t>2026-06-05</t>
-  </si>
-  <si>
-    <t>17:18:02</t>
-  </si>
-  <si>
-    <t>2026-06-05 17:18:09</t>
-  </si>
-  <si>
-    <t>12:28:04</t>
-  </si>
-  <si>
-    <t>2026-06-05 12:28:11</t>
-  </si>
-  <si>
-    <t>12:04:00</t>
-  </si>
-  <si>
-    <t>2026-06-05 12:04:07</t>
-  </si>
-  <si>
-    <t>07:42:26</t>
-  </si>
-  <si>
-    <t>2026-06-05 07:42:33</t>
-  </si>
-  <si>
-    <t>2026-06-04</t>
-  </si>
-  <si>
-    <t>17:06:06</t>
-  </si>
-  <si>
-    <t>2026-06-04 17:06:03</t>
-  </si>
-  <si>
-    <t>12:23:09</t>
-  </si>
-  <si>
-    <t>2026-06-04 12:23:16</t>
-  </si>
-  <si>
-    <t>12:01:40</t>
-  </si>
-  <si>
-    <t>2026-06-04 12:01:37</t>
-  </si>
-  <si>
-    <t>07:50:13</t>
-  </si>
-  <si>
-    <t>2026-06-04 07:50:20</t>
-  </si>
-  <si>
-    <t>2026-06-03</t>
-  </si>
-  <si>
-    <t>17:02:33</t>
-  </si>
-  <si>
-    <t>2026-06-03 17:02:40</t>
-  </si>
-  <si>
-    <t>12:31:26</t>
-  </si>
-  <si>
-    <t>2026-06-03 12:31:32</t>
-  </si>
-  <si>
-    <t>12:02:33</t>
-  </si>
-  <si>
-    <t>2026-06-03 12:02:37</t>
-  </si>
-  <si>
-    <t>07:49:18</t>
-  </si>
-  <si>
-    <t>2026-06-03 07:49:22</t>
-  </si>
-  <si>
-    <t>2026-06-02</t>
-  </si>
-  <si>
-    <t>17:03:41</t>
-  </si>
-  <si>
-    <t>2026-06-02 17:03:44</t>
-  </si>
-  <si>
-    <t>12:31:14</t>
-  </si>
-  <si>
-    <t>2026-06-02 13:41:40</t>
-  </si>
-  <si>
-    <t>12:02:05</t>
-  </si>
-  <si>
-    <t>2026-06-02 13:41:02</t>
-  </si>
-  <si>
-    <t>07:49:37</t>
-  </si>
-  <si>
-    <t>2026-06-02 13:41:36</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>17:04:04</t>
-  </si>
-  <si>
-    <t>12:28:09</t>
-  </si>
-  <si>
-    <t>2026-06-02 13:41:15</t>
-  </si>
-  <si>
-    <t>12:02:44</t>
-  </si>
-  <si>
-    <t>2026-06-02 13:41:11</t>
-  </si>
-  <si>
-    <t>07:42:19</t>
-  </si>
-  <si>
-    <t>2026-06-02 13:41:10</t>
-  </si>
-  <si>
-    <t>2026-05-30</t>
-  </si>
-  <si>
-    <t>12:03:46</t>
-  </si>
-  <si>
-    <t>2026-05-30 12:03:47</t>
-  </si>
-  <si>
-    <t>07:48:32</t>
-  </si>
-  <si>
-    <t>2026-05-30 07:48:36</t>
-  </si>
-  <si>
-    <t>2026-05-29</t>
-  </si>
-  <si>
-    <t>17:05:25</t>
-  </si>
-  <si>
-    <t>2026-05-29 17:05:27</t>
-  </si>
-  <si>
-    <t>12:33:58</t>
-  </si>
-  <si>
-    <t>2026-05-29 12:34:02</t>
-  </si>
-  <si>
-    <t>2026-05-29 12:04:02</t>
-  </si>
-  <si>
-    <t>08:19:00</t>
-  </si>
-  <si>
-    <t>2026-05-29 08:19:05</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="197">
+  <si>
+    <t xml:space="preserve">Transaction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employee ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Department</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Punch Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Punch State</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Serial Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Device Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upload Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actual Temperature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6140</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:38:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check In</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main Office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5870221760077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HR Office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24 07:37:57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:08:40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5870201460003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Board/Function Room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23 17:08:37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:50:02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23 12:50:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:03:36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23 12:03:33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:39:13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23 07:39:11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:04:21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-22 17:04:18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:28:46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-22 12:28:44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:04:11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-22 12:04:09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:03:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-22 07:03:48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:00:41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-20 17:00:41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:33:11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-20 12:33:09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:04:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-20 12:04:06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:38:11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-20 07:38:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:03:12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-19 17:03:14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:21:14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-19 12:21:17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:01:25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-19 12:01:27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:42:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-19 07:42:48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:07:14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18 17:07:18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:18:19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18 12:18:23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:01:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18 12:01:54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:38:13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18 07:38:13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:12:11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-17 17:12:04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:40:25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-17 12:40:17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:01:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-17 12:01:38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:09:24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-17 07:09:24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:01:51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15 17:01:47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:35:41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15 12:35:36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:05:08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15 12:05:09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:02:02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15 07:02:02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:03:04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-13 17:03:02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:28:49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-13 12:28:49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:03:23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-13 12:03:21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:32:56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-13 07:32:57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:02:06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11 17:02:08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:43:24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11 12:43:22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:04:39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11 12:04:37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:29:20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11 07:29:25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:05:14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-10 17:05:13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:26:42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-10 12:26:47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:03:09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-10 12:03:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:24:24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-10 07:24:28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:04:55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09 17:04:55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:30:06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09 12:30:13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:04:01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09 12:04:06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:48:51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09 07:48:57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:01:36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08 17:01:42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:29:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08 12:29:41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:03:37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08 12:03:28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:13:36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08 07:13:43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:02:21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-06 17:02:27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:32:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-06 12:32:22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:02:55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-06 12:03:01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:46:03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-06 07:46:09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:18:02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05 17:18:09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:28:04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05 12:28:11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:04:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05 12:04:07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:42:26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05 07:42:33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:06:06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04 17:06:03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:23:09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04 12:23:16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:01:40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04 12:01:37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:50:13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04 07:50:20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:02:33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-03 17:02:40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:31:26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-03 12:31:32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:02:33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-03 12:02:37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:49:18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-03 07:49:22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:03:41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02 17:03:44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:31:14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02 13:41:40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:02:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02 13:41:02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:49:37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02 13:41:36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:04:04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:28:09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02 13:41:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:02:44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02 13:41:11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:42:19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-02 13:41:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:03:46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-30 12:03:47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:48:32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-30 07:48:36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:05:25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29 17:05:27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:33:58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29 12:34:02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29 12:04:02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08:19:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-29 08:19:05</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="16"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -648,96 +668,114 @@
     </fill>
   </fills>
   <borders count="3">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="1f497d"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="eeece1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4f81bd"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="c0504d"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="9bbb59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="8064a2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4bacc6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="f79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000ff"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -745,265 +783,155 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
-                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
-                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
-                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K82"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:K1048576"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" customWidth="1"/>
-    <col min="9" max="9" width="20.7109375" customWidth="1"/>
-    <col min="10" max="10" width="20.7109375" customWidth="1"/>
-    <col min="11" max="11" width="19.7109375" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="11.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="12.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="20.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="19.72"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1018,7 +946,7 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1053,7 +981,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
@@ -1084,7 +1012,7 @@
       </c>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
@@ -1115,7 +1043,7 @@
       </c>
       <c r="K4" s="2"/>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
@@ -1146,7 +1074,7 @@
       </c>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -1177,7 +1105,7 @@
       </c>
       <c r="K6" s="2"/>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
@@ -1208,7 +1136,7 @@
       </c>
       <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
         <v>12</v>
       </c>
@@ -1239,7 +1167,7 @@
       </c>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
@@ -1270,7 +1198,7 @@
       </c>
       <c r="K9" s="2"/>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
@@ -1301,7 +1229,7 @@
       </c>
       <c r="K10" s="2"/>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
@@ -1332,7 +1260,7 @@
       </c>
       <c r="K11" s="2"/>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
         <v>12</v>
       </c>
@@ -1363,7 +1291,7 @@
       </c>
       <c r="K12" s="2"/>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
@@ -1394,7 +1322,7 @@
       </c>
       <c r="K13" s="2"/>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
@@ -1425,7 +1353,7 @@
       </c>
       <c r="K14" s="2"/>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
         <v>12</v>
       </c>
@@ -1456,7 +1384,7 @@
       </c>
       <c r="K15" s="2"/>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
         <v>12</v>
       </c>
@@ -1487,7 +1415,7 @@
       </c>
       <c r="K16" s="2"/>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
         <v>12</v>
       </c>
@@ -1518,7 +1446,7 @@
       </c>
       <c r="K17" s="2"/>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
         <v>12</v>
       </c>
@@ -1549,7 +1477,7 @@
       </c>
       <c r="K18" s="2"/>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
         <v>12</v>
       </c>
@@ -1580,7 +1508,7 @@
       </c>
       <c r="K19" s="2"/>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
         <v>12</v>
       </c>
@@ -1611,7 +1539,7 @@
       </c>
       <c r="K20" s="2"/>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
         <v>12</v>
       </c>
@@ -1642,7 +1570,7 @@
       </c>
       <c r="K21" s="2"/>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
         <v>12</v>
       </c>
@@ -1673,7 +1601,7 @@
       </c>
       <c r="K22" s="2"/>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
         <v>12</v>
       </c>
@@ -1704,7 +1632,7 @@
       </c>
       <c r="K23" s="2"/>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
         <v>12</v>
       </c>
@@ -1735,7 +1663,7 @@
       </c>
       <c r="K24" s="2"/>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
         <v>12</v>
       </c>
@@ -1766,7 +1694,7 @@
       </c>
       <c r="K25" s="2"/>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
         <v>12</v>
       </c>
@@ -1797,7 +1725,7 @@
       </c>
       <c r="K26" s="2"/>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
         <v>12</v>
       </c>
@@ -1828,7 +1756,7 @@
       </c>
       <c r="K27" s="2"/>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
         <v>12</v>
       </c>
@@ -1859,7 +1787,7 @@
       </c>
       <c r="K28" s="2"/>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
         <v>12</v>
       </c>
@@ -1890,7 +1818,7 @@
       </c>
       <c r="K29" s="2"/>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
         <v>12</v>
       </c>
@@ -1921,7 +1849,7 @@
       </c>
       <c r="K30" s="2"/>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
         <v>12</v>
       </c>
@@ -1952,7 +1880,7 @@
       </c>
       <c r="K31" s="2"/>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
         <v>12</v>
       </c>
@@ -1983,7 +1911,7 @@
       </c>
       <c r="K32" s="2"/>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
         <v>12</v>
       </c>
@@ -2014,7 +1942,7 @@
       </c>
       <c r="K33" s="2"/>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
         <v>12</v>
       </c>
@@ -2045,7 +1973,7 @@
       </c>
       <c r="K34" s="2"/>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
         <v>12</v>
       </c>
@@ -2076,7 +2004,7 @@
       </c>
       <c r="K35" s="2"/>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
         <v>12</v>
       </c>
@@ -2107,7 +2035,7 @@
       </c>
       <c r="K36" s="2"/>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
         <v>12</v>
       </c>
@@ -2138,7 +2066,7 @@
       </c>
       <c r="K37" s="2"/>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
         <v>12</v>
       </c>
@@ -2169,7 +2097,7 @@
       </c>
       <c r="K38" s="2"/>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
         <v>12</v>
       </c>
@@ -2200,7 +2128,7 @@
       </c>
       <c r="K39" s="2"/>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
         <v>12</v>
       </c>
@@ -2231,7 +2159,7 @@
       </c>
       <c r="K40" s="2"/>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
         <v>12</v>
       </c>
@@ -2262,7 +2190,7 @@
       </c>
       <c r="K41" s="2"/>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
         <v>12</v>
       </c>
@@ -2293,7 +2221,7 @@
       </c>
       <c r="K42" s="2"/>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
         <v>12</v>
       </c>
@@ -2324,7 +2252,7 @@
       </c>
       <c r="K43" s="2"/>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
         <v>12</v>
       </c>
@@ -2355,7 +2283,7 @@
       </c>
       <c r="K44" s="2"/>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
         <v>12</v>
       </c>
@@ -2376,17 +2304,17 @@
         <v>16</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>117</v>
       </c>
       <c r="K45" s="2"/>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
         <v>12</v>
       </c>
@@ -2401,7 +2329,7 @@
         <v>118</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>16</v>
@@ -2417,7 +2345,7 @@
       </c>
       <c r="K46" s="2"/>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
         <v>12</v>
       </c>
@@ -2432,7 +2360,7 @@
         <v>120</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>16</v>
@@ -2448,7 +2376,7 @@
       </c>
       <c r="K47" s="2"/>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
         <v>12</v>
       </c>
@@ -2457,13 +2385,13 @@
         <v>3</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>16</v>
@@ -2475,11 +2403,11 @@
         <v>18</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K48" s="2"/>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
         <v>12</v>
       </c>
@@ -2488,13 +2416,13 @@
         <v>3</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>125</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>16</v>
@@ -2510,7 +2438,7 @@
       </c>
       <c r="K49" s="2"/>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
         <v>12</v>
       </c>
@@ -2519,29 +2447,29 @@
         <v>3</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>127</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>128</v>
       </c>
       <c r="K50" s="2"/>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
         <v>12</v>
       </c>
@@ -2550,29 +2478,29 @@
         <v>3</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>129</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>130</v>
       </c>
       <c r="K51" s="2"/>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
         <v>12</v>
       </c>
@@ -2581,13 +2509,13 @@
         <v>3</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>16</v>
@@ -2599,11 +2527,11 @@
         <v>18</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K52" s="2"/>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
         <v>12</v>
       </c>
@@ -2612,13 +2540,13 @@
         <v>3</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>134</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>16</v>
@@ -2634,7 +2562,7 @@
       </c>
       <c r="K53" s="2"/>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
         <v>12</v>
       </c>
@@ -2643,13 +2571,13 @@
         <v>3</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>136</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>16</v>
@@ -2665,7 +2593,7 @@
       </c>
       <c r="K54" s="2"/>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
         <v>12</v>
       </c>
@@ -2674,13 +2602,13 @@
         <v>3</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>138</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>16</v>
@@ -2696,7 +2624,7 @@
       </c>
       <c r="K55" s="2"/>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
         <v>12</v>
       </c>
@@ -2705,13 +2633,13 @@
         <v>3</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>16</v>
@@ -2723,11 +2651,11 @@
         <v>18</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K56" s="2"/>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
         <v>12</v>
       </c>
@@ -2736,13 +2664,13 @@
         <v>3</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>143</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>16</v>
@@ -2758,7 +2686,7 @@
       </c>
       <c r="K57" s="2"/>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
         <v>12</v>
       </c>
@@ -2767,13 +2695,13 @@
         <v>3</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>145</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>16</v>
@@ -2789,7 +2717,7 @@
       </c>
       <c r="K58" s="2"/>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
         <v>12</v>
       </c>
@@ -2798,13 +2726,13 @@
         <v>3</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>147</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>16</v>
@@ -2820,7 +2748,7 @@
       </c>
       <c r="K59" s="2"/>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
         <v>12</v>
       </c>
@@ -2829,29 +2757,29 @@
         <v>3</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K60" s="2"/>
     </row>
-    <row r="61" spans="1:11">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
         <v>12</v>
       </c>
@@ -2860,29 +2788,29 @@
         <v>3</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>153</v>
       </c>
       <c r="K61" s="2"/>
     </row>
-    <row r="62" spans="1:11">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
         <v>12</v>
       </c>
@@ -2891,29 +2819,29 @@
         <v>3</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>154</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>155</v>
       </c>
       <c r="K62" s="2"/>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
         <v>12</v>
       </c>
@@ -2922,29 +2850,29 @@
         <v>3</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>156</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>157</v>
       </c>
       <c r="K63" s="2"/>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
         <v>12</v>
       </c>
@@ -2953,13 +2881,13 @@
         <v>3</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>16</v>
@@ -2971,11 +2899,11 @@
         <v>18</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K64" s="2"/>
     </row>
-    <row r="65" spans="1:11">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="s">
         <v>12</v>
       </c>
@@ -2984,13 +2912,13 @@
         <v>3</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>161</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>16</v>
@@ -3006,7 +2934,7 @@
       </c>
       <c r="K65" s="2"/>
     </row>
-    <row r="66" spans="1:11">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="s">
         <v>12</v>
       </c>
@@ -3015,13 +2943,13 @@
         <v>3</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>163</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>16</v>
@@ -3037,7 +2965,7 @@
       </c>
       <c r="K66" s="2"/>
     </row>
-    <row r="67" spans="1:11">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2" t="s">
         <v>12</v>
       </c>
@@ -3046,13 +2974,13 @@
         <v>3</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>165</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>16</v>
@@ -3068,7 +2996,7 @@
       </c>
       <c r="K67" s="2"/>
     </row>
-    <row r="68" spans="1:11">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2" t="s">
         <v>12</v>
       </c>
@@ -3077,13 +3005,13 @@
         <v>3</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>16</v>
@@ -3095,11 +3023,11 @@
         <v>18</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K68" s="2"/>
     </row>
-    <row r="69" spans="1:11">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2" t="s">
         <v>12</v>
       </c>
@@ -3108,13 +3036,13 @@
         <v>3</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>170</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>16</v>
@@ -3130,7 +3058,7 @@
       </c>
       <c r="K69" s="2"/>
     </row>
-    <row r="70" spans="1:11">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
         <v>12</v>
       </c>
@@ -3139,29 +3067,29 @@
         <v>3</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>172</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>173</v>
       </c>
       <c r="K70" s="2"/>
     </row>
-    <row r="71" spans="1:11">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="s">
         <v>12</v>
       </c>
@@ -3170,29 +3098,29 @@
         <v>3</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>174</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>175</v>
       </c>
       <c r="K71" s="2"/>
     </row>
-    <row r="72" spans="1:11">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2" t="s">
         <v>12</v>
       </c>
@@ -3201,29 +3129,29 @@
         <v>3</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="K72" s="2"/>
     </row>
-    <row r="73" spans="1:11">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2" t="s">
         <v>12</v>
       </c>
@@ -3232,29 +3160,29 @@
         <v>3</v>
       </c>
       <c r="D73" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E73" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E73" s="2" t="s">
+      <c r="F73" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J73" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="F73" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G73" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H73" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I73" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J73" s="2" t="s">
-        <v>175</v>
-      </c>
       <c r="K73" s="2"/>
     </row>
-    <row r="74" spans="1:11">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
         <v>12</v>
       </c>
@@ -3263,13 +3191,13 @@
         <v>3</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>180</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>16</v>
@@ -3285,7 +3213,7 @@
       </c>
       <c r="K74" s="2"/>
     </row>
-    <row r="75" spans="1:11">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
         <v>12</v>
       </c>
@@ -3294,13 +3222,13 @@
         <v>3</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>182</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>16</v>
@@ -3316,7 +3244,7 @@
       </c>
       <c r="K75" s="2"/>
     </row>
-    <row r="76" spans="1:11">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
         <v>12</v>
       </c>
@@ -3325,29 +3253,29 @@
         <v>3</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K76" s="2"/>
     </row>
-    <row r="77" spans="1:11">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2" t="s">
         <v>12</v>
       </c>
@@ -3356,29 +3284,29 @@
         <v>3</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>187</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>188</v>
       </c>
       <c r="K77" s="2"/>
     </row>
-    <row r="78" spans="1:11">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="s">
         <v>12</v>
       </c>
@@ -3387,29 +3315,29 @@
         <v>3</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K78" s="2"/>
     </row>
-    <row r="79" spans="1:11">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
         <v>12</v>
       </c>
@@ -3418,29 +3346,29 @@
         <v>3</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>192</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>193</v>
       </c>
       <c r="K79" s="2"/>
     </row>
-    <row r="80" spans="1:11">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2" t="s">
         <v>12</v>
       </c>
@@ -3449,29 +3377,29 @@
         <v>3</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E80" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J80" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="F80" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G80" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>195</v>
-      </c>
       <c r="K80" s="2"/>
     </row>
-    <row r="81" spans="1:11">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2" t="s">
         <v>12</v>
       </c>
@@ -3480,10 +3408,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>22</v>
@@ -3492,51 +3420,27 @@
         <v>16</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>196</v>
       </c>
       <c r="K81" s="2"/>
     </row>
-    <row r="82" spans="1:11">
-      <c r="A82" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B82" s="2"/>
-      <c r="C82" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="F82" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G82" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H82" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I82" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J82" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="K82" s="2"/>
-    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>